--- a/textual data analysis/artifacts/reports/paired_bootstrap/paired_bootstrap_best_runs_combined_summary.xlsx
+++ b/textual data analysis/artifacts/reports/paired_bootstrap/paired_bootstrap_best_runs_combined_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF5"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,646 +436,721 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>svm_run_tag</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mnir_run_tag</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>svm_run_dir</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>mnir_run_dir</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>dataset_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>remove_leakage</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>text_version</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>svm_representation</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>mnir_representation</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>svm_chi2_k</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>svm_c</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>mnir_chi2_k</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mnir_svm_c</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>svm_class_weight</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>random_seed</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>split_id</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>parameter_source</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>label_view_for_modeling</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>n_test</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>n_bootstrap</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>bootstrap_method</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ci_method</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>confidence_level</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>bootstrap_random_seed</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>all_classes_present</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>n_invalid_resamples</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>svm_macro_f1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>mnir_svm_macro_f1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>delta_svm_minus_mnir</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ci_2.5%</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>ci_97.5%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>ci_excludes_0</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>n_test</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>n_bootstrap</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>bootstrap_method</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>ci_method</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>confidence_level</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>bootstrap_random_seed</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>all_classes_present</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>n_invalid_resamples</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>svm_chi2_k</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>svm_c</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>mnir_chi2_k</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mnir_svm_c</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>parameter_source</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>label_view_for_modeling</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>svm_run_dir</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>mnir_run_dir</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>interpretation_scope</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>table_4_3_svm_macro_f1</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>table_4_3_mnir_macro_f1</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>svm_matches_table_4_3</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>mnir_matches_table_4_3</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>??</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>admin_bow_full_20260703_predictions</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>admin_bow_full_20260703_predictions</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>D:\Github\Personal-Project\textual data analysis\artifacts\reports\administrative_win_lose_mixed\no_leakage\bow\step3_runs\admin_bow_full_20260703_predictions</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>D:\Github\Personal-Project\textual data analysis\artifacts\reports\administrative_win_lose_mixed\no_leakage\bow\step3_runs\admin_bow_full_20260703_predictions</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>administrative_win_lose_mixed</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>no_leakage</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>bow</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>bow</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0.3916739438371886</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.3183707292197858</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0733032146174028</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.0440559556725411</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.1042617750386292</v>
-      </c>
-      <c r="K2" t="b">
-        <v>1</v>
+      <c r="K2" t="n">
+        <v>3000</v>
       </c>
       <c r="L2" t="n">
-        <v>2263</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>5000</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>random_state_42_train0.7_val0.1_test0.2</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>saved_step3_test_predictions</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>2263</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>stratified_paired</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>percentile</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="X2" t="n">
         <v>0.95</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Y2" t="n">
         <v>20260703</v>
       </c>
-      <c r="R2" t="b">
+      <c r="Z2" t="b">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AA2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="n">
-        <v>3000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>4</v>
-      </c>
-      <c r="V2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>fixed_best_run_configs</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>..\artifacts\reports\administrative_win_lose_mixed\no_leakage\bow\step3_runs\full_20260504_154912</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>..\artifacts\reports\administrative_win_lose_mixed\no_leakage\bow\step3_runs\full_20260504_154912</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" t="n">
+        <v>0.3916739438371886</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.3183707292197858</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.0733032146174028</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.0440559556725411</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.1042617750386292</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>fixed trained models and fixed test set only</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>administrative_win_lose_mixed_no_leakage_svm_bow_mnir_bow_class_weight_none_best_runs_paired_bootstrap_summary.csv</t>
         </is>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.380459</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.318371</v>
-      </c>
-      <c r="AE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>??</t>
+          <t>civil</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>full_20260504_154912</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_20260504_154912</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>..\artifacts\reports\civil_win_lose_mixed\no_leakage\tfidf\step3_runs\full_20260504_154912</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>..\artifacts\reports\civil_win_lose_mixed\no_leakage\tfidf\step3_runs\full_20260504_154912</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>civil_win_lose_mixed</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>no_leakage</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>tfidf</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>tfidf</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="K3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>random_state_42_train0.7_val0.1_test0.2</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>fixed_best_run_configs</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>1133</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>stratified_paired</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>percentile</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>20260703</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
         <v>0.4277972992985715</v>
       </c>
-      <c r="G3" t="n">
+      <c r="AC3" t="n">
         <v>0.3525234025234025</v>
       </c>
-      <c r="H3" t="n">
+      <c r="AD3" t="n">
         <v>0.07527389677516889</v>
       </c>
-      <c r="I3" t="n">
+      <c r="AE3" t="n">
         <v>0.0363772129272566</v>
       </c>
-      <c r="J3" t="n">
+      <c r="AF3" t="n">
         <v>0.1150396599529879</v>
       </c>
-      <c r="K3" t="b">
+      <c r="AG3" t="b">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>1133</v>
-      </c>
-      <c r="M3" t="n">
-        <v>5000</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>stratified_paired</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>percentile</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>20260703</v>
-      </c>
-      <c r="R3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>5000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>4</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>fixed_best_run_configs</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>..\artifacts\reports\civil_win_lose_mixed\no_leakage\tfidf\step3_runs\full_20260504_154912</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>..\artifacts\reports\civil_win_lose_mixed\no_leakage\tfidf\step3_runs\full_20260504_154912</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>fixed trained models and fixed test set only</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>civil_win_lose_mixed_no_leakage_svm_tfidf_mnir_tfidf_class_weight_none_best_runs_paired_bootstrap_summary.csv</t>
         </is>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.427797</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.352523</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>??</t>
+          <t>criminal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>full_20260504_154912</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_20260504_154912</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>..\artifacts\reports\criminal_win_lose_mixed\no_leakage\tf\step3_runs\full_20260504_154912</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>..\artifacts\reports\criminal_win_lose_mixed\no_leakage\tfidf\step3_runs\full_20260504_154912</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>criminal_win_lose_mixed</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>no_leakage</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>tf</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>tfidf</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>0.5772699607148786</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.3902188337587152</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.1870511269561633</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.1235104949115566</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.2601531201728231</v>
-      </c>
-      <c r="K4" t="b">
-        <v>1</v>
+      <c r="K4" t="n">
+        <v>5000</v>
       </c>
       <c r="L4" t="n">
-        <v>5227</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
         <v>5000</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>random_state_42_train0.7_val0.1_test0.2</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>fixed_best_run_configs</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>legacy_defendant_view_then_claimant_view_output</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>5227</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>stratified_paired</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>percentile</t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="X4" t="n">
         <v>0.95</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Y4" t="n">
         <v>20260703</v>
       </c>
-      <c r="R4" t="b">
+      <c r="Z4" t="b">
         <v>1</v>
       </c>
-      <c r="S4" t="n">
+      <c r="AA4" t="n">
         <v>0</v>
       </c>
-      <c r="T4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>4</v>
-      </c>
-      <c r="V4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>fixed_best_run_configs</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>legacy_defendant_view_then_claimant_view_output</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>..\artifacts\reports\criminal_win_lose_mixed\no_leakage\tf\step3_runs\full_20260504_154912</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>..\artifacts\reports\criminal_win_lose_mixed\no_leakage\tfidf\step3_runs\full_20260504_154912</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB4" t="n">
+        <v>0.5772699607148786</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.3902188337587152</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.1870511269561633</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1235104949115566</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.2601531201728231</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>fixed trained models and fixed test set only</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>criminal_win_lose_mixed_no_leakage_svm_tf_mnir_tfidf_class_weight_none_best_runs_paired_bootstrap_summary.csv</t>
         </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.5772699999999999</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.390219</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>??????</t>
+          <t>cwc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>full_20260504_154912</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_20260504_154912</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>..\artifacts\reports\cwc_win_lose_mixed\no_leakage\bow\step3_runs\full_20260504_154912</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>..\artifacts\reports\cwc_win_lose_mixed\no_leakage\tf\step3_runs\full_20260504_154912</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>cwc_win_lose_mixed</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>no_leakage</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>bow</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>tf</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="K5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>random_state_42_train0.7_val0.1_test0.2</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>fixed_best_run_configs</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>362</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>stratified_paired</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>percentile</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>20260703</v>
+      </c>
+      <c r="Z5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
         <v>0.6541390103070531</v>
       </c>
-      <c r="G5" t="n">
+      <c r="AC5" t="n">
         <v>0.5453635934281825</v>
       </c>
-      <c r="H5" t="n">
+      <c r="AD5" t="n">
         <v>0.1087754168788706</v>
       </c>
-      <c r="I5" t="n">
+      <c r="AE5" t="n">
         <v>0.0065510551826554</v>
       </c>
-      <c r="J5" t="n">
+      <c r="AF5" t="n">
         <v>0.2464769533033176</v>
       </c>
-      <c r="K5" t="b">
+      <c r="AG5" t="b">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>362</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>stratified_paired</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>percentile</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>20260703</v>
-      </c>
-      <c r="R5" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>fixed_best_run_configs</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>current</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>..\artifacts\reports\cwc_win_lose_mixed\no_leakage\bow\step3_runs\full_20260504_154912</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>..\artifacts\reports\cwc_win_lose_mixed\no_leakage\tf\step3_runs\full_20260504_154912</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>fixed trained models and fixed test set only</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>cwc_win_lose_mixed_no_leakage_svm_bow_mnir_tf_class_weight_none_best_runs_paired_bootstrap_summary.csv</t>
         </is>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.654139</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.545364</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
